--- a/DevSim/Templates/Symmetry_Breaking_Template/UserParams.xlsx
+++ b/DevSim/Templates/Symmetry_Breaking_Template/UserParams.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/glennshields/Desktop/NewTemplates/Symmetry_Breaking_Template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/glenn/Desktop/DevSim/Templates/Symmetry_Breaking_Template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCCA70AA-B01E-814F-B109-48327170C4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0E101C-6B66-B24D-845E-9DEA6A01B671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.20250000000000001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -594,7 +594,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.13350000000000001</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
